--- a/assets/documents/project-planning.xlsx
+++ b/assets/documents/project-planning.xlsx
@@ -410,17 +410,7 @@
     <t>Record of metadata</t>
   </si>
   <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">Chiriandreses Museum — Methodology &amp; Paradata </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>Documentation.md</t>
-    </r>
+    <t>CM-D001 META/PARADATA DIGITISATION RECORDS.xlsx</t>
   </si>
   <si>
     <t>Record of paradata</t>
@@ -436,7 +426,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -490,10 +480,6 @@
       <u/>
       <color rgb="FF0000FF"/>
       <name val="&quot;Roboto Condensed&quot;"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -627,7 +613,7 @@
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4194,8 +4180,7 @@
   <hyperlinks>
     <hyperlink r:id="rId1" ref="D21"/>
     <hyperlink r:id="rId2" ref="B26"/>
-    <hyperlink r:id="rId3" ref="B36"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>